--- a/results/reports/year_2021_report.xlsx
+++ b/results/reports/year_2021_report.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:T2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,30 +505,40 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>top_30_return_compounded</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>top_30_excess</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>decile_return_compounded</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>decile_excess</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>OMXS30_return</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>OMXC25_return</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>OMXH25_return</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>OSEBX_return</t>
         </is>
@@ -572,21 +582,27 @@
         <v>49.77</v>
       </c>
       <c r="M2" t="n">
+        <v>42.87</v>
+      </c>
+      <c r="N2" t="n">
+        <v>43.59</v>
+      </c>
+      <c r="O2" t="n">
         <v>41.19</v>
       </c>
-      <c r="N2" t="n">
+      <c r="P2" t="n">
         <v>41.91</v>
       </c>
-      <c r="O2" t="n">
+      <c r="Q2" t="n">
         <v>10.35</v>
       </c>
-      <c r="P2" t="n">
+      <c r="R2" t="n">
         <v>16.32</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="S2" t="n">
         <v>13</v>
       </c>
-      <c r="R2" t="n">
+      <c r="T2" t="n">
         <v>13.46</v>
       </c>
     </row>
@@ -687,7 +703,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6503111366284894</v>
+        <v>0.6503111366284893</v>
       </c>
       <c r="E4" t="n">
         <v>5.6805</v>
@@ -707,7 +723,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6437906581342593</v>
+        <v>0.6437906581342594</v>
       </c>
       <c r="E5" t="n">
         <v>4.4691</v>
@@ -727,7 +743,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6407358741888194</v>
+        <v>0.6407358741888196</v>
       </c>
       <c r="E6" t="n">
         <v>-1.2531</v>
@@ -747,7 +763,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6400655449062591</v>
+        <v>0.6400655449062593</v>
       </c>
       <c r="E7" t="n">
         <v>4.3223</v>
@@ -767,7 +783,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6383659467893807</v>
+        <v>0.638365946789381</v>
       </c>
       <c r="E8" t="n">
         <v>1.8692</v>
@@ -787,7 +803,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.6372736392250142</v>
+        <v>0.6372736392250143</v>
       </c>
       <c r="E9" t="n">
         <v>0.9798</v>
@@ -827,7 +843,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6288128864172158</v>
+        <v>0.6288128864172157</v>
       </c>
       <c r="E11" t="n">
         <v>0.5748</v>
@@ -847,7 +863,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6258549148308112</v>
+        <v>0.6258549148308111</v>
       </c>
       <c r="E12" t="n">
         <v>0.4207</v>
@@ -887,7 +903,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6159215480708337</v>
+        <v>0.6159215480708338</v>
       </c>
       <c r="E14" t="n">
         <v>1.8713</v>
@@ -947,7 +963,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6094117293621718</v>
+        <v>0.6094117293621719</v>
       </c>
       <c r="E17" t="n">
         <v>3.6243</v>
@@ -967,7 +983,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.6075493577642044</v>
+        <v>0.6075493577642043</v>
       </c>
       <c r="E18" t="n">
         <v>20.6897</v>
@@ -987,7 +1003,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.6067955694003033</v>
+        <v>0.6067955694003034</v>
       </c>
       <c r="E19" t="n">
         <v>8.1076</v>
@@ -1007,7 +1023,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.6067067566736158</v>
+        <v>0.6067067566736157</v>
       </c>
       <c r="E20" t="n">
         <v>0.1111</v>
@@ -1093,7 +1109,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.6955770056387028</v>
+        <v>0.6955770056387029</v>
       </c>
       <c r="E2" t="n">
         <v>-15.7571</v>
@@ -1233,7 +1249,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.6731327374354409</v>
+        <v>0.673132737435441</v>
       </c>
       <c r="E9" t="n">
         <v>-14.415</v>
@@ -1273,7 +1289,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6664101288364256</v>
+        <v>0.6664101288364255</v>
       </c>
       <c r="E11" t="n">
         <v>11.5756</v>
@@ -1313,7 +1329,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.6565226897592457</v>
+        <v>0.6565226897592455</v>
       </c>
       <c r="E13" t="n">
         <v>-13.3486</v>
@@ -1333,7 +1349,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6545202701750967</v>
+        <v>0.6545202701750966</v>
       </c>
       <c r="E14" t="n">
         <v>-14.8655</v>
@@ -1353,7 +1369,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.654492111982664</v>
+        <v>0.6544921119826641</v>
       </c>
       <c r="E15" t="n">
         <v>-2.0257</v>
@@ -1373,7 +1389,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.6451704264322157</v>
+        <v>0.6451704264322159</v>
       </c>
       <c r="E16" t="n">
         <v>-7.6557</v>
@@ -1579,7 +1595,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6583226722817399</v>
+        <v>0.65832267228174</v>
       </c>
       <c r="E4" t="n">
         <v>5.6323</v>
@@ -1639,7 +1655,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6471425924237384</v>
+        <v>0.6471425924237383</v>
       </c>
       <c r="E7" t="n">
         <v>2.2257</v>
@@ -1679,7 +1695,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.643908328431069</v>
+        <v>0.6439083284310689</v>
       </c>
       <c r="E9" t="n">
         <v>-0.2061</v>
@@ -1839,7 +1855,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6186748377547368</v>
+        <v>0.6186748377547366</v>
       </c>
       <c r="E17" t="n">
         <v>-6.1224</v>
@@ -1859,7 +1875,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.617788112643824</v>
+        <v>0.6177881126438242</v>
       </c>
       <c r="E18" t="n">
         <v>17.3129</v>
@@ -1899,7 +1915,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.6167308457083888</v>
+        <v>0.6167308457083887</v>
       </c>
       <c r="E20" t="n">
         <v>5.7292</v>
@@ -1985,7 +2001,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.7145145956458117</v>
+        <v>0.7145145956458119</v>
       </c>
       <c r="E2" t="n">
         <v>3.1667</v>
@@ -2025,7 +2041,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6637777877286879</v>
+        <v>0.6637777877286881</v>
       </c>
       <c r="E4" t="n">
         <v>2.0179</v>
@@ -2105,7 +2121,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6290684682643273</v>
+        <v>0.6290684682643274</v>
       </c>
       <c r="E8" t="n">
         <v>7.1812</v>
@@ -2125,7 +2141,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.6273293936360271</v>
+        <v>0.6273293936360272</v>
       </c>
       <c r="E9" t="n">
         <v>-5.3442</v>
@@ -2185,7 +2201,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6237694260971098</v>
+        <v>0.6237694260971097</v>
       </c>
       <c r="E12" t="n">
         <v>11.7666</v>
@@ -2285,7 +2301,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6055691825349588</v>
+        <v>0.6055691825349589</v>
       </c>
       <c r="E17" t="n">
         <v>0.9366</v>
@@ -2345,7 +2361,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.6044655609007483</v>
+        <v>0.6044655609007482</v>
       </c>
       <c r="E20" t="n">
         <v>5.1852</v>
@@ -2571,7 +2587,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.6548956152225596</v>
+        <v>0.6548956152225597</v>
       </c>
       <c r="E9" t="n">
         <v>-3.4317</v>
@@ -2591,7 +2607,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.654010221971441</v>
+        <v>0.6540102219714409</v>
       </c>
       <c r="E10" t="n">
         <v>3.2821</v>
@@ -2651,7 +2667,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.6507996223182583</v>
+        <v>0.6507996223182585</v>
       </c>
       <c r="E13" t="n">
         <v>1.4579</v>
@@ -2671,7 +2687,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6481470331215441</v>
+        <v>0.6481470331215442</v>
       </c>
       <c r="E14" t="n">
         <v>-0.1393</v>
@@ -2751,7 +2767,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.6439928680326991</v>
+        <v>0.6439928680326992</v>
       </c>
       <c r="E18" t="n">
         <v>4.5011</v>
@@ -2957,7 +2973,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6206435556080042</v>
+        <v>0.6206435556080043</v>
       </c>
       <c r="E6" t="n">
         <v>-0.7487</v>
@@ -2977,7 +2993,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6196315106105091</v>
+        <v>0.619631510610509</v>
       </c>
       <c r="E7" t="n">
         <v>2.5067</v>
@@ -3017,7 +3033,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.6172836609389122</v>
+        <v>0.6172836609389121</v>
       </c>
       <c r="E9" t="n">
         <v>-2.0768</v>
@@ -3117,7 +3133,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6118179196549235</v>
+        <v>0.6118179196549234</v>
       </c>
       <c r="E14" t="n">
         <v>-2.3013</v>
@@ -3177,7 +3193,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6074356004718982</v>
+        <v>0.607435600471898</v>
       </c>
       <c r="E17" t="n">
         <v>1.3423</v>
@@ -3217,7 +3233,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.6055013573538865</v>
+        <v>0.6055013573538864</v>
       </c>
       <c r="E19" t="n">
         <v>0.45</v>
@@ -3237,7 +3253,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.6050116535108042</v>
+        <v>0.6050116535108041</v>
       </c>
       <c r="E20" t="n">
         <v>-6.0995</v>
@@ -3277,7 +3293,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3298,25 +3314,30 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>top_30_return</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>decile_return</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>OMXS30</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>OMXC25</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>OMXH25</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>OSEBX</t>
         </is>
@@ -3333,12 +3354,15 @@
         <v>8.27</v>
       </c>
       <c r="D2" t="n">
+        <v>6.61</v>
+      </c>
+      <c r="E2" t="n">
         <v>6.06</v>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -3351,12 +3375,15 @@
         <v>1.2</v>
       </c>
       <c r="D3" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="E3" t="n">
         <v>4.18</v>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -3369,12 +3396,15 @@
         <v>6.65</v>
       </c>
       <c r="D4" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="E4" t="n">
         <v>6.42</v>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -3387,18 +3417,21 @@
         <v>4.46</v>
       </c>
       <c r="D5" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="E5" t="n">
         <v>2.96</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>1.1</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>4.53</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>3.83</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>1.66</v>
       </c>
     </row>
@@ -3413,18 +3446,21 @@
         <v>2.74</v>
       </c>
       <c r="D6" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="E6" t="n">
         <v>2.31</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>1.12</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>1.51</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>0.75</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>2.8</v>
       </c>
     </row>
@@ -3439,18 +3475,21 @@
         <v>8.01</v>
       </c>
       <c r="D7" t="n">
+        <v>8.82</v>
+      </c>
+      <c r="E7" t="n">
         <v>8.039999999999999</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>0.95</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>3.76</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>3.37</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>1.3</v>
       </c>
     </row>
@@ -3465,18 +3504,21 @@
         <v>2.51</v>
       </c>
       <c r="D8" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="E8" t="n">
         <v>1.71</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>4.72</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>3.5</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>5.52</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>1.19</v>
       </c>
     </row>
@@ -3491,18 +3533,21 @@
         <v>-3.36</v>
       </c>
       <c r="D9" t="n">
+        <v>-2.38</v>
+      </c>
+      <c r="E9" t="n">
         <v>-3.64</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>-0.79</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>2.58</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>0.78</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>0.67</v>
       </c>
     </row>
@@ -3517,18 +3562,21 @@
         <v>5.95</v>
       </c>
       <c r="D10" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="E10" t="n">
         <v>6.28</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>-3.92</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>-4.79</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>-5.66</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>1.88</v>
       </c>
     </row>
@@ -3543,18 +3591,21 @@
         <v>3.12</v>
       </c>
       <c r="D11" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="E11" t="n">
         <v>1.26</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>1.4</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>4.82</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>0.74</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>2.53</v>
       </c>
     </row>
@@ -3569,18 +3620,21 @@
         <v>1.96</v>
       </c>
       <c r="D12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="E12" t="n">
         <v>2.81</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>-2.15</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>-4.5</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>-1.62</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>-0.96</v>
       </c>
     </row>
@@ -3595,18 +3649,21 @@
         <v>-0.28</v>
       </c>
       <c r="D13" t="n">
+        <v>-3.21</v>
+      </c>
+      <c r="E13" t="n">
         <v>-2.7</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>7.94</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>4.41</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>5.11</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>1.71</v>
       </c>
     </row>
@@ -3933,7 +3990,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6278165378897703</v>
+        <v>0.6278165378897702</v>
       </c>
       <c r="E4" t="n">
         <v>11.9036</v>
@@ -3953,7 +4010,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6260872358592023</v>
+        <v>0.6260872358592025</v>
       </c>
       <c r="E5" t="n">
         <v>9.665100000000001</v>
@@ -4053,7 +4110,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6060420404692913</v>
+        <v>0.6060420404692912</v>
       </c>
       <c r="E10" t="n">
         <v>4.7515</v>
@@ -4073,7 +4130,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6016558292729738</v>
+        <v>0.6016558292729739</v>
       </c>
       <c r="E11" t="n">
         <v>-5.4606</v>
@@ -4153,7 +4210,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.5957238766512216</v>
+        <v>0.5957238766512215</v>
       </c>
       <c r="E15" t="n">
         <v>-3.3923</v>
@@ -4193,7 +4250,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.5892511740555582</v>
+        <v>0.5892511740555583</v>
       </c>
       <c r="E17" t="n">
         <v>-9.365</v>
@@ -4233,7 +4290,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.5881723824969837</v>
+        <v>0.5881723824969838</v>
       </c>
       <c r="E19" t="n">
         <v>1.1179</v>
@@ -4253,7 +4310,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.5881485019203798</v>
+        <v>0.5881485019203797</v>
       </c>
       <c r="E20" t="n">
         <v>20.3788</v>
@@ -4273,7 +4330,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.5856709547643425</v>
+        <v>0.5856709547643426</v>
       </c>
       <c r="E21" t="n">
         <v>7.6772</v>
@@ -4339,7 +4396,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.6226661628875741</v>
+        <v>0.6226661628875743</v>
       </c>
       <c r="E2" t="n">
         <v>26.4238</v>
@@ -4359,7 +4416,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.6184895238364058</v>
+        <v>0.6184895238364055</v>
       </c>
       <c r="E3" t="n">
         <v>14.2568</v>
@@ -4419,7 +4476,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6061415382358432</v>
+        <v>0.6061415382358433</v>
       </c>
       <c r="E6" t="n">
         <v>-94.9173</v>
@@ -4439,7 +4496,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6025844949362948</v>
+        <v>0.602584494936295</v>
       </c>
       <c r="E7" t="n">
         <v>-1.9416</v>
@@ -4519,7 +4576,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6013809520351487</v>
+        <v>0.6013809520351486</v>
       </c>
       <c r="E11" t="n">
         <v>-3.0079</v>
@@ -4539,7 +4596,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6006466263433246</v>
+        <v>0.6006466263433248</v>
       </c>
       <c r="E12" t="n">
         <v>1.2415</v>
@@ -4619,7 +4676,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.5968456053442546</v>
+        <v>0.5968456053442545</v>
       </c>
       <c r="E16" t="n">
         <v>-5.2588</v>
@@ -4659,7 +4716,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.5932945290053446</v>
+        <v>0.5932945290053445</v>
       </c>
       <c r="E18" t="n">
         <v>3.4866</v>
@@ -4845,7 +4902,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6250718396165219</v>
+        <v>0.6250718396165218</v>
       </c>
       <c r="E5" t="n">
         <v>1.8711</v>
@@ -4905,7 +4962,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6204414807901363</v>
+        <v>0.6204414807901364</v>
       </c>
       <c r="E8" t="n">
         <v>4.0339</v>
@@ -5105,7 +5162,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.6009975928125406</v>
+        <v>0.6009975928125407</v>
       </c>
       <c r="E18" t="n">
         <v>2.9293</v>
@@ -5165,7 +5222,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.599042756159745</v>
+        <v>0.5990427561597451</v>
       </c>
       <c r="E21" t="n">
         <v>37.0741</v>
@@ -5291,7 +5348,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6153071382371167</v>
+        <v>0.6153071382371166</v>
       </c>
       <c r="E5" t="n">
         <v>10.9967</v>
@@ -5351,7 +5408,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6102505900093074</v>
+        <v>0.6102505900093073</v>
       </c>
       <c r="E8" t="n">
         <v>-1.3456</v>
@@ -5451,7 +5508,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.6050853529077606</v>
+        <v>0.6050853529077604</v>
       </c>
       <c r="E13" t="n">
         <v>0.8001</v>
@@ -5611,7 +5668,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.5962812933892476</v>
+        <v>0.5962812933892477</v>
       </c>
       <c r="E21" t="n">
         <v>3.1558</v>
@@ -5677,7 +5734,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.6593432261743363</v>
+        <v>0.6593432261743364</v>
       </c>
       <c r="E2" t="n">
         <v>0.3655</v>
@@ -5717,7 +5774,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6252168739572418</v>
+        <v>0.6252168739572419</v>
       </c>
       <c r="E4" t="n">
         <v>-2.0988</v>
@@ -6183,7 +6240,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6549125265006747</v>
+        <v>0.6549125265006746</v>
       </c>
       <c r="E5" t="n">
         <v>5.98</v>
@@ -6203,7 +6260,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6494597639002179</v>
+        <v>0.649459763900218</v>
       </c>
       <c r="E6" t="n">
         <v>10.5769</v>
@@ -6223,7 +6280,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6463318035984387</v>
+        <v>0.6463318035984388</v>
       </c>
       <c r="E7" t="n">
         <v>10.9619</v>
@@ -6283,7 +6340,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6455788523259325</v>
+        <v>0.6455788523259324</v>
       </c>
       <c r="E10" t="n">
         <v>1.2626</v>
@@ -6323,7 +6380,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6398436543991912</v>
+        <v>0.6398436543991911</v>
       </c>
       <c r="E12" t="n">
         <v>5.9836</v>
@@ -6363,7 +6420,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6305038003571327</v>
+        <v>0.6305038003571328</v>
       </c>
       <c r="E14" t="n">
         <v>12.9692</v>

--- a/results/reports/year_2021_report.xlsx
+++ b/results/reports/year_2021_report.xlsx
@@ -703,7 +703,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6503111366284893</v>
+        <v>0.6503111366284894</v>
       </c>
       <c r="E4" t="n">
         <v>5.6805</v>
@@ -743,7 +743,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6407358741888196</v>
+        <v>0.6407358741888194</v>
       </c>
       <c r="E6" t="n">
         <v>-1.2531</v>
@@ -763,7 +763,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6400655449062593</v>
+        <v>0.6400655449062591</v>
       </c>
       <c r="E7" t="n">
         <v>4.3223</v>
@@ -783,7 +783,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.638365946789381</v>
+        <v>0.6383659467893809</v>
       </c>
       <c r="E8" t="n">
         <v>1.8692</v>
@@ -803,7 +803,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.6372736392250143</v>
+        <v>0.6372736392250142</v>
       </c>
       <c r="E9" t="n">
         <v>0.9798</v>
@@ -843,7 +843,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6288128864172157</v>
+        <v>0.6288128864172158</v>
       </c>
       <c r="E11" t="n">
         <v>0.5748</v>
@@ -863,7 +863,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6258549148308111</v>
+        <v>0.6258549148308112</v>
       </c>
       <c r="E12" t="n">
         <v>0.4207</v>
@@ -883,7 +883,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.6226764498827013</v>
+        <v>0.6226764498827012</v>
       </c>
       <c r="E13" t="n">
         <v>2.1563</v>
@@ -903,7 +903,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6159215480708338</v>
+        <v>0.6159215480708337</v>
       </c>
       <c r="E14" t="n">
         <v>1.8713</v>
@@ -963,7 +963,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6094117293621719</v>
+        <v>0.6094117293621718</v>
       </c>
       <c r="E17" t="n">
         <v>3.6243</v>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.6067955694003034</v>
+        <v>0.6067955694003033</v>
       </c>
       <c r="E19" t="n">
         <v>8.1076</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6891058309818583</v>
+        <v>0.6891058309818581</v>
       </c>
       <c r="E4" t="n">
         <v>13.7365</v>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6832949521072754</v>
+        <v>0.6832949521072753</v>
       </c>
       <c r="E7" t="n">
         <v>4.1915</v>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6810738570677884</v>
+        <v>0.6810738570677886</v>
       </c>
       <c r="E8" t="n">
         <v>-6.8767</v>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6698948825707663</v>
+        <v>0.6698948825707661</v>
       </c>
       <c r="E10" t="n">
         <v>11.4823</v>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.6565226897592455</v>
+        <v>0.6565226897592457</v>
       </c>
       <c r="E13" t="n">
         <v>-13.3486</v>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6545202701750966</v>
+        <v>0.6545202701750967</v>
       </c>
       <c r="E14" t="n">
         <v>-14.8655</v>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.6451704264322159</v>
+        <v>0.6451704264322157</v>
       </c>
       <c r="E16" t="n">
         <v>-7.6557</v>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.6397951073352043</v>
+        <v>0.6397951073352042</v>
       </c>
       <c r="E18" t="n">
         <v>4.7478</v>
@@ -1655,7 +1655,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6471425924237383</v>
+        <v>0.6471425924237384</v>
       </c>
       <c r="E7" t="n">
         <v>2.2257</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.6201219947681752</v>
+        <v>0.6201219947681751</v>
       </c>
       <c r="E15" t="n">
         <v>14.8971</v>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6186748377547366</v>
+        <v>0.6186748377547368</v>
       </c>
       <c r="E17" t="n">
         <v>-6.1224</v>
@@ -1895,7 +1895,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.616925473625585</v>
+        <v>0.6169254736255851</v>
       </c>
       <c r="E19" t="n">
         <v>7.0919</v>
@@ -2021,7 +2021,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.6716563783882118</v>
+        <v>0.6716563783882117</v>
       </c>
       <c r="E3" t="n">
         <v>-0.06370000000000001</v>
@@ -2061,7 +2061,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6544123049060147</v>
+        <v>0.6544123049060149</v>
       </c>
       <c r="E5" t="n">
         <v>-0.3972</v>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6532720284588132</v>
+        <v>0.653272028458813</v>
       </c>
       <c r="E6" t="n">
         <v>-0.2545</v>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6460347425734176</v>
+        <v>0.6460347425734178</v>
       </c>
       <c r="E7" t="n">
         <v>4.5551</v>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6290684682643274</v>
+        <v>0.6290684682643273</v>
       </c>
       <c r="E8" t="n">
         <v>7.1812</v>
@@ -2161,7 +2161,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6265482582297751</v>
+        <v>0.6265482582297749</v>
       </c>
       <c r="E10" t="n">
         <v>4.5446</v>
@@ -2201,7 +2201,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6237694260971097</v>
+        <v>0.6237694260971098</v>
       </c>
       <c r="E12" t="n">
         <v>11.7666</v>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.6044655609007482</v>
+        <v>0.6044655609007483</v>
       </c>
       <c r="E20" t="n">
         <v>5.1852</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6753631833305067</v>
+        <v>0.6753631833305066</v>
       </c>
       <c r="E6" t="n">
         <v>3.5714</v>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6529618787411163</v>
+        <v>0.6529618787411162</v>
       </c>
       <c r="E11" t="n">
         <v>3.9468</v>
@@ -2647,7 +2647,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6521564396861916</v>
+        <v>0.6521564396861915</v>
       </c>
       <c r="E12" t="n">
         <v>4.8858</v>
@@ -2667,7 +2667,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.6507996223182585</v>
+        <v>0.6507996223182583</v>
       </c>
       <c r="E13" t="n">
         <v>1.4579</v>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6481470331215442</v>
+        <v>0.6481470331215441</v>
       </c>
       <c r="E14" t="n">
         <v>-0.1393</v>
@@ -2727,7 +2727,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.6452255059713192</v>
+        <v>0.6452255059713194</v>
       </c>
       <c r="E16" t="n">
         <v>1.9704</v>
@@ -2767,7 +2767,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.6439928680326992</v>
+        <v>0.6439928680326991</v>
       </c>
       <c r="E18" t="n">
         <v>4.5011</v>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.723752548570856</v>
+        <v>0.7237525485708562</v>
       </c>
       <c r="E2" t="n">
         <v>7.4005</v>
@@ -2913,7 +2913,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.6586614508939383</v>
+        <v>0.6586614508939382</v>
       </c>
       <c r="E3" t="n">
         <v>-3.1733</v>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6206435556080043</v>
+        <v>0.6206435556080042</v>
       </c>
       <c r="E6" t="n">
         <v>-0.7487</v>
@@ -3133,7 +3133,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6118179196549234</v>
+        <v>0.6118179196549235</v>
       </c>
       <c r="E14" t="n">
         <v>-2.3013</v>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.6087580211239655</v>
+        <v>0.6087580211239654</v>
       </c>
       <c r="E16" t="n">
         <v>-1.2188</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.606515054803266</v>
+        <v>0.6065150548032661</v>
       </c>
       <c r="E18" t="n">
         <v>-1.9417</v>
@@ -3253,7 +3253,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.6050116535108041</v>
+        <v>0.605011653510804</v>
       </c>
       <c r="E20" t="n">
         <v>-6.0995</v>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.6317003915941549</v>
+        <v>0.631700391594155</v>
       </c>
       <c r="E3" t="n">
         <v>28.9278</v>
@@ -3990,7 +3990,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6278165378897702</v>
+        <v>0.6278165378897704</v>
       </c>
       <c r="E4" t="n">
         <v>11.9036</v>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6260872358592025</v>
+        <v>0.6260872358592023</v>
       </c>
       <c r="E5" t="n">
         <v>9.665100000000001</v>
@@ -4090,7 +4090,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.6070602961748603</v>
+        <v>0.6070602961748605</v>
       </c>
       <c r="E9" t="n">
         <v>12.5389</v>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.5957238766512215</v>
+        <v>0.5957238766512216</v>
       </c>
       <c r="E15" t="n">
         <v>-3.3923</v>
@@ -4270,7 +4270,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.5889822204366317</v>
+        <v>0.5889822204366318</v>
       </c>
       <c r="E18" t="n">
         <v>7.44</v>
@@ -4290,7 +4290,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.5881723824969838</v>
+        <v>0.5881723824969837</v>
       </c>
       <c r="E19" t="n">
         <v>1.1179</v>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.5881485019203797</v>
+        <v>0.5881485019203798</v>
       </c>
       <c r="E20" t="n">
         <v>20.3788</v>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.5856709547643426</v>
+        <v>0.5856709547643425</v>
       </c>
       <c r="E21" t="n">
         <v>7.6772</v>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6118036867163528</v>
+        <v>0.6118036867163529</v>
       </c>
       <c r="E4" t="n">
         <v>3.8871</v>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6061415382358433</v>
+        <v>0.6061415382358432</v>
       </c>
       <c r="E6" t="n">
         <v>-94.9173</v>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6013809520351486</v>
+        <v>0.6013809520351487</v>
       </c>
       <c r="E11" t="n">
         <v>-3.0079</v>
@@ -4596,7 +4596,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6006466263433248</v>
+        <v>0.6006466263433247</v>
       </c>
       <c r="E12" t="n">
         <v>1.2415</v>
@@ -4616,7 +4616,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.6004191949003387</v>
+        <v>0.6004191949003386</v>
       </c>
       <c r="E13" t="n">
         <v>12.8182</v>
@@ -4676,7 +4676,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.5968456053442545</v>
+        <v>0.5968456053442547</v>
       </c>
       <c r="E16" t="n">
         <v>-5.2588</v>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6204414807901364</v>
+        <v>0.6204414807901363</v>
       </c>
       <c r="E8" t="n">
         <v>4.0339</v>
@@ -5162,7 +5162,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.6009975928125407</v>
+        <v>0.6009975928125406</v>
       </c>
       <c r="E18" t="n">
         <v>2.9293</v>
@@ -5222,7 +5222,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.5990427561597451</v>
+        <v>0.599042756159745</v>
       </c>
       <c r="E21" t="n">
         <v>37.0741</v>
@@ -5288,7 +5288,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.6591216453197423</v>
+        <v>0.6591216453197424</v>
       </c>
       <c r="E2" t="n">
         <v>4.9214</v>
@@ -5408,7 +5408,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6102505900093073</v>
+        <v>0.6102505900093074</v>
       </c>
       <c r="E8" t="n">
         <v>-1.3456</v>
@@ -5508,7 +5508,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.6050853529077604</v>
+        <v>0.6050853529077606</v>
       </c>
       <c r="E13" t="n">
         <v>0.8001</v>
@@ -5734,7 +5734,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.6593432261743364</v>
+        <v>0.6593432261743363</v>
       </c>
       <c r="E2" t="n">
         <v>0.3655</v>
@@ -5754,7 +5754,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.6295459249370924</v>
+        <v>0.6295459249370923</v>
       </c>
       <c r="E3" t="n">
         <v>8.1038</v>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.615619666813355</v>
+        <v>0.6156196668133549</v>
       </c>
       <c r="E10" t="n">
         <v>-5.83</v>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.6061408799696818</v>
+        <v>0.6061408799696817</v>
       </c>
       <c r="E18" t="n">
         <v>7.2216</v>
@@ -6220,7 +6220,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6556588246512915</v>
+        <v>0.6556588246512913</v>
       </c>
       <c r="E4" t="n">
         <v>15.4134</v>
@@ -6240,7 +6240,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6549125265006746</v>
+        <v>0.6549125265006747</v>
       </c>
       <c r="E5" t="n">
         <v>5.98</v>
@@ -6260,7 +6260,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.649459763900218</v>
+        <v>0.6494597639002179</v>
       </c>
       <c r="E6" t="n">
         <v>10.5769</v>
@@ -6280,7 +6280,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6463318035984388</v>
+        <v>0.6463318035984387</v>
       </c>
       <c r="E7" t="n">
         <v>10.9619</v>
@@ -6340,7 +6340,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6455788523259324</v>
+        <v>0.6455788523259323</v>
       </c>
       <c r="E10" t="n">
         <v>1.2626</v>
@@ -6400,7 +6400,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.6318466916989546</v>
+        <v>0.6318466916989547</v>
       </c>
       <c r="E13" t="n">
         <v>7.8745</v>
@@ -6420,7 +6420,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6305038003571328</v>
+        <v>0.6305038003571327</v>
       </c>
       <c r="E14" t="n">
         <v>12.9692</v>

--- a/results/reports/year_2021_report.xlsx
+++ b/results/reports/year_2021_report.xlsx
@@ -594,16 +594,16 @@
         <v>41.91</v>
       </c>
       <c r="Q2" t="n">
-        <v>10.35</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="R2" t="n">
-        <v>16.32</v>
+        <v>11.28</v>
       </c>
       <c r="S2" t="n">
-        <v>13</v>
+        <v>8.83</v>
       </c>
       <c r="T2" t="n">
-        <v>13.46</v>
+        <v>11.61</v>
       </c>
     </row>
   </sheetData>
@@ -703,7 +703,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6503111366284894</v>
+        <v>0.6503111366284893</v>
       </c>
       <c r="E4" t="n">
         <v>5.6805</v>
@@ -723,7 +723,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6437906581342594</v>
+        <v>0.6437906581342593</v>
       </c>
       <c r="E5" t="n">
         <v>4.4691</v>
@@ -763,7 +763,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6400655449062591</v>
+        <v>0.640065544906259</v>
       </c>
       <c r="E7" t="n">
         <v>4.3223</v>
@@ -783,7 +783,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6383659467893809</v>
+        <v>0.638365946789381</v>
       </c>
       <c r="E8" t="n">
         <v>1.8692</v>
@@ -883,7 +883,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.6226764498827012</v>
+        <v>0.6226764498827013</v>
       </c>
       <c r="E13" t="n">
         <v>2.1563</v>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6863294615059283</v>
+        <v>0.6863294615059281</v>
       </c>
       <c r="E5" t="n">
         <v>12.2797</v>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6810738570677886</v>
+        <v>0.6810738570677884</v>
       </c>
       <c r="E8" t="n">
         <v>-6.8767</v>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6698948825707661</v>
+        <v>0.6698948825707663</v>
       </c>
       <c r="E10" t="n">
         <v>11.4823</v>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6664101288364255</v>
+        <v>0.6664101288364256</v>
       </c>
       <c r="E11" t="n">
         <v>11.5756</v>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6545202701750967</v>
+        <v>0.6545202701750966</v>
       </c>
       <c r="E14" t="n">
         <v>-14.8655</v>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.6544921119826641</v>
+        <v>0.654492111982664</v>
       </c>
       <c r="E15" t="n">
         <v>-2.0257</v>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.6397951073352042</v>
+        <v>0.6397951073352043</v>
       </c>
       <c r="E18" t="n">
         <v>4.7478</v>
@@ -1489,7 +1489,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.6290425825088248</v>
+        <v>0.6290425825088249</v>
       </c>
       <c r="E21" t="n">
         <v>4.6679</v>
@@ -1595,7 +1595,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.65832267228174</v>
+        <v>0.6583226722817399</v>
       </c>
       <c r="E4" t="n">
         <v>5.6323</v>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.6177881126438242</v>
+        <v>0.617788112643824</v>
       </c>
       <c r="E18" t="n">
         <v>17.3129</v>
@@ -1895,7 +1895,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.6169254736255851</v>
+        <v>0.616925473625585</v>
       </c>
       <c r="E19" t="n">
         <v>7.0919</v>
@@ -2021,7 +2021,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.6716563783882117</v>
+        <v>0.6716563783882118</v>
       </c>
       <c r="E3" t="n">
         <v>-0.06370000000000001</v>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6637777877286881</v>
+        <v>0.6637777877286879</v>
       </c>
       <c r="E4" t="n">
         <v>2.0179</v>
@@ -2061,7 +2061,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6544123049060149</v>
+        <v>0.6544123049060147</v>
       </c>
       <c r="E5" t="n">
         <v>-0.3972</v>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.653272028458813</v>
+        <v>0.6532720284588132</v>
       </c>
       <c r="E6" t="n">
         <v>-0.2545</v>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6460347425734178</v>
+        <v>0.6460347425734176</v>
       </c>
       <c r="E7" t="n">
         <v>4.5551</v>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6290684682643273</v>
+        <v>0.6290684682643274</v>
       </c>
       <c r="E8" t="n">
         <v>7.1812</v>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.6273293936360272</v>
+        <v>0.6273293936360271</v>
       </c>
       <c r="E9" t="n">
         <v>-5.3442</v>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.6044655609007483</v>
+        <v>0.6044655609007482</v>
       </c>
       <c r="E20" t="n">
         <v>5.1852</v>
@@ -2467,7 +2467,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.7025698583609755</v>
+        <v>0.7025698583609757</v>
       </c>
       <c r="E3" t="n">
         <v>6.8768</v>
@@ -2507,7 +2507,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6814500466212398</v>
+        <v>0.6814500466212396</v>
       </c>
       <c r="E5" t="n">
         <v>2.7065</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6753631833305066</v>
+        <v>0.6753631833305067</v>
       </c>
       <c r="E6" t="n">
         <v>3.5714</v>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.6548956152225597</v>
+        <v>0.6548956152225598</v>
       </c>
       <c r="E9" t="n">
         <v>-3.4317</v>
@@ -2607,7 +2607,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6540102219714409</v>
+        <v>0.654010221971441</v>
       </c>
       <c r="E10" t="n">
         <v>3.2821</v>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6529618787411162</v>
+        <v>0.6529618787411163</v>
       </c>
       <c r="E11" t="n">
         <v>3.9468</v>
@@ -2647,7 +2647,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6521564396861915</v>
+        <v>0.6521564396861916</v>
       </c>
       <c r="E12" t="n">
         <v>4.8858</v>
@@ -2667,7 +2667,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.6507996223182583</v>
+        <v>0.6507996223182585</v>
       </c>
       <c r="E13" t="n">
         <v>1.4579</v>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6481470331215441</v>
+        <v>0.6481470331215442</v>
       </c>
       <c r="E14" t="n">
         <v>-0.1393</v>
@@ -2767,7 +2767,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.6439928680326991</v>
+        <v>0.6439928680326992</v>
       </c>
       <c r="E18" t="n">
         <v>4.5011</v>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.6419364922365811</v>
+        <v>0.641936492236581</v>
       </c>
       <c r="E19" t="n">
         <v>-0.9429999999999999</v>
@@ -2913,7 +2913,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.6586614508939382</v>
+        <v>0.6586614508939383</v>
       </c>
       <c r="E3" t="n">
         <v>-3.1733</v>
@@ -3073,7 +3073,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6150296857988884</v>
+        <v>0.6150296857988886</v>
       </c>
       <c r="E11" t="n">
         <v>5.1363</v>
@@ -3133,7 +3133,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6118179196549235</v>
+        <v>0.6118179196549234</v>
       </c>
       <c r="E14" t="n">
         <v>-2.3013</v>
@@ -3193,7 +3193,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.607435600471898</v>
+        <v>0.6074356004718982</v>
       </c>
       <c r="E17" t="n">
         <v>1.3423</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.6065150548032661</v>
+        <v>0.606515054803266</v>
       </c>
       <c r="E18" t="n">
         <v>-1.9417</v>
@@ -3422,18 +3422,10 @@
       <c r="E5" t="n">
         <v>2.96</v>
       </c>
-      <c r="F5" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="G5" t="n">
-        <v>4.53</v>
-      </c>
-      <c r="H5" t="n">
-        <v>3.83</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1.66</v>
-      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -3970,7 +3962,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.631700391594155</v>
+        <v>0.6317003915941549</v>
       </c>
       <c r="E3" t="n">
         <v>28.9278</v>
@@ -3990,7 +3982,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6278165378897704</v>
+        <v>0.6278165378897702</v>
       </c>
       <c r="E4" t="n">
         <v>11.9036</v>
@@ -4170,7 +4162,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.5988491443018787</v>
+        <v>0.5988491443018789</v>
       </c>
       <c r="E13" t="n">
         <v>33.2761</v>
@@ -4250,7 +4242,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.5892511740555583</v>
+        <v>0.5892511740555582</v>
       </c>
       <c r="E17" t="n">
         <v>-9.365</v>
@@ -4270,7 +4262,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.5889822204366318</v>
+        <v>0.5889822204366317</v>
       </c>
       <c r="E18" t="n">
         <v>7.44</v>
@@ -4496,7 +4488,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.602584494936295</v>
+        <v>0.6025844949362948</v>
       </c>
       <c r="E7" t="n">
         <v>-1.9416</v>
@@ -4536,7 +4528,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.6022141646943332</v>
+        <v>0.6022141646943331</v>
       </c>
       <c r="E9" t="n">
         <v>8.6111</v>
@@ -4556,7 +4548,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6019069281308006</v>
+        <v>0.6019069281308004</v>
       </c>
       <c r="E10" t="n">
         <v>5.9241</v>
@@ -4576,7 +4568,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6013809520351487</v>
+        <v>0.6013809520351486</v>
       </c>
       <c r="E11" t="n">
         <v>-3.0079</v>
@@ -4596,7 +4588,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6006466263433247</v>
+        <v>0.6006466263433248</v>
       </c>
       <c r="E12" t="n">
         <v>1.2415</v>
@@ -4656,7 +4648,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.5976829695464562</v>
+        <v>0.5976829695464563</v>
       </c>
       <c r="E15" t="n">
         <v>-4.8667</v>
@@ -4676,7 +4668,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.5968456053442547</v>
+        <v>0.5968456053442546</v>
       </c>
       <c r="E16" t="n">
         <v>-5.2588</v>
@@ -4696,7 +4688,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.5960586487923986</v>
+        <v>0.5960586487923984</v>
       </c>
       <c r="E17" t="n">
         <v>2.2351</v>
@@ -4882,7 +4874,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6262241578210671</v>
+        <v>0.626224157821067</v>
       </c>
       <c r="E4" t="n">
         <v>12.5696</v>
@@ -5082,7 +5074,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6113145694477687</v>
+        <v>0.6113145694477686</v>
       </c>
       <c r="E14" t="n">
         <v>0.1821</v>
@@ -5102,7 +5094,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.6074673188749944</v>
+        <v>0.6074673188749943</v>
       </c>
       <c r="E15" t="n">
         <v>6.7078</v>
@@ -5162,7 +5154,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.6009975928125406</v>
+        <v>0.6009975928125407</v>
       </c>
       <c r="E18" t="n">
         <v>2.9293</v>
@@ -5222,7 +5214,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.599042756159745</v>
+        <v>0.5990427561597451</v>
       </c>
       <c r="E21" t="n">
         <v>37.0741</v>
@@ -5348,7 +5340,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6153071382371166</v>
+        <v>0.6153071382371167</v>
       </c>
       <c r="E5" t="n">
         <v>10.9967</v>
@@ -5388,7 +5380,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6113374455829967</v>
+        <v>0.6113374455829966</v>
       </c>
       <c r="E7" t="n">
         <v>4.3062</v>
@@ -5468,7 +5460,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6062628799474944</v>
+        <v>0.6062628799474943</v>
       </c>
       <c r="E11" t="n">
         <v>6.4162</v>
@@ -5488,7 +5480,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6056172129990115</v>
+        <v>0.6056172129990116</v>
       </c>
       <c r="E12" t="n">
         <v>10.3369</v>
@@ -5528,7 +5520,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6044695116989472</v>
+        <v>0.6044695116989474</v>
       </c>
       <c r="E14" t="n">
         <v>0.4085</v>
@@ -5568,7 +5560,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.6020418943203893</v>
+        <v>0.6020418943203895</v>
       </c>
       <c r="E16" t="n">
         <v>2.8772</v>
@@ -5668,7 +5660,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.5962812933892477</v>
+        <v>0.5962812933892476</v>
       </c>
       <c r="E21" t="n">
         <v>3.1558</v>
@@ -5754,7 +5746,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.6295459249370923</v>
+        <v>0.6295459249370924</v>
       </c>
       <c r="E3" t="n">
         <v>8.1038</v>
@@ -5774,7 +5766,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6252168739572419</v>
+        <v>0.6252168739572418</v>
       </c>
       <c r="E4" t="n">
         <v>-2.0988</v>
@@ -5874,7 +5866,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.6161188024740963</v>
+        <v>0.6161188024740962</v>
       </c>
       <c r="E9" t="n">
         <v>-6.0081</v>
@@ -5894,7 +5886,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6156196668133549</v>
+        <v>0.615619666813355</v>
       </c>
       <c r="E10" t="n">
         <v>-5.83</v>
@@ -5934,7 +5926,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6119014277699597</v>
+        <v>0.6119014277699598</v>
       </c>
       <c r="E12" t="n">
         <v>1.7496</v>
@@ -6014,7 +6006,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.6074211988028989</v>
+        <v>0.607421198802899</v>
       </c>
       <c r="E16" t="n">
         <v>-6.2664</v>
@@ -6054,7 +6046,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.6061408799696817</v>
+        <v>0.6061408799696818</v>
       </c>
       <c r="E18" t="n">
         <v>7.2216</v>
@@ -6200,7 +6192,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.6596788510577438</v>
+        <v>0.6596788510577437</v>
       </c>
       <c r="E3" t="n">
         <v>10.5753</v>
@@ -6220,7 +6212,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6556588246512913</v>
+        <v>0.6556588246512915</v>
       </c>
       <c r="E4" t="n">
         <v>15.4134</v>
@@ -6240,7 +6232,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6549125265006747</v>
+        <v>0.6549125265006746</v>
       </c>
       <c r="E5" t="n">
         <v>5.98</v>
@@ -6260,7 +6252,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6494597639002179</v>
+        <v>0.649459763900218</v>
       </c>
       <c r="E6" t="n">
         <v>10.5769</v>
@@ -6300,7 +6292,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6461806717076048</v>
+        <v>0.646180671707605</v>
       </c>
       <c r="E8" t="n">
         <v>5.9626</v>
@@ -6340,7 +6332,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6455788523259323</v>
+        <v>0.6455788523259324</v>
       </c>
       <c r="E10" t="n">
         <v>1.2626</v>
@@ -6380,7 +6372,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6398436543991911</v>
+        <v>0.6398436543991912</v>
       </c>
       <c r="E12" t="n">
         <v>5.9836</v>
@@ -6440,7 +6432,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.6278601283865832</v>
+        <v>0.6278601283865833</v>
       </c>
       <c r="E15" t="n">
         <v>-1.6949</v>
@@ -6460,7 +6452,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.6271311884420855</v>
+        <v>0.6271311884420856</v>
       </c>
       <c r="E16" t="n">
         <v>8.374000000000001</v>
@@ -6480,7 +6472,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6229084286729044</v>
+        <v>0.6229084286729043</v>
       </c>
       <c r="E17" t="n">
         <v>4.4746</v>

--- a/results/reports/year_2021_report.xlsx
+++ b/results/reports/year_2021_report.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.6658852262573489</v>
+        <v>0.6658852262573488</v>
       </c>
       <c r="E2" t="n">
         <v>2.8224</v>
@@ -683,7 +683,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.6525996215190331</v>
+        <v>0.6525996215190333</v>
       </c>
       <c r="E3" t="n">
         <v>2.0023</v>
@@ -703,7 +703,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6503111366284893</v>
+        <v>0.6503111366284894</v>
       </c>
       <c r="E4" t="n">
         <v>5.6805</v>
@@ -723,7 +723,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6437906581342593</v>
+        <v>0.6437906581342594</v>
       </c>
       <c r="E5" t="n">
         <v>4.4691</v>
@@ -763,7 +763,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.640065544906259</v>
+        <v>0.6400655449062591</v>
       </c>
       <c r="E7" t="n">
         <v>4.3223</v>
@@ -783,7 +783,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.638365946789381</v>
+        <v>0.6383659467893807</v>
       </c>
       <c r="E8" t="n">
         <v>1.8692</v>
@@ -883,7 +883,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.6226764498827013</v>
+        <v>0.6226764498827012</v>
       </c>
       <c r="E13" t="n">
         <v>2.1563</v>
@@ -983,7 +983,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.6075493577642043</v>
+        <v>0.6075493577642044</v>
       </c>
       <c r="E18" t="n">
         <v>20.6897</v>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.6067067566736157</v>
+        <v>0.6067067566736158</v>
       </c>
       <c r="E20" t="n">
         <v>0.1111</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6891058309818581</v>
+        <v>0.6891058309818583</v>
       </c>
       <c r="E4" t="n">
         <v>13.7365</v>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6863294615059281</v>
+        <v>0.6863294615059283</v>
       </c>
       <c r="E5" t="n">
         <v>12.2797</v>
@@ -1249,7 +1249,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.673132737435441</v>
+        <v>0.6731327374354409</v>
       </c>
       <c r="E9" t="n">
         <v>-14.415</v>
@@ -1309,7 +1309,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6581377089397171</v>
+        <v>0.6581377089397169</v>
       </c>
       <c r="E12" t="n">
         <v>-16.8769</v>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.654492111982664</v>
+        <v>0.6544921119826641</v>
       </c>
       <c r="E15" t="n">
         <v>-2.0257</v>
@@ -1489,7 +1489,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.6290425825088249</v>
+        <v>0.6290425825088248</v>
       </c>
       <c r="E21" t="n">
         <v>4.6679</v>
@@ -1695,7 +1695,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.6439083284310689</v>
+        <v>0.643908328431069</v>
       </c>
       <c r="E9" t="n">
         <v>-0.2061</v>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.617788112643824</v>
+        <v>0.6177881126438242</v>
       </c>
       <c r="E18" t="n">
         <v>17.3129</v>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6637777877286879</v>
+        <v>0.6637777877286881</v>
       </c>
       <c r="E4" t="n">
         <v>2.0179</v>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6290684682643274</v>
+        <v>0.6290684682643273</v>
       </c>
       <c r="E8" t="n">
         <v>7.1812</v>
@@ -2161,7 +2161,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6265482582297749</v>
+        <v>0.626548258229775</v>
       </c>
       <c r="E10" t="n">
         <v>4.5446</v>
@@ -2281,7 +2281,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.6066284001996152</v>
+        <v>0.6066284001996154</v>
       </c>
       <c r="E16" t="n">
         <v>-4.2689</v>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.6044655609007482</v>
+        <v>0.6044655609007483</v>
       </c>
       <c r="E20" t="n">
         <v>5.1852</v>
@@ -2467,7 +2467,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.7025698583609757</v>
+        <v>0.7025698583609755</v>
       </c>
       <c r="E3" t="n">
         <v>6.8768</v>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.6548956152225598</v>
+        <v>0.6548956152225596</v>
       </c>
       <c r="E9" t="n">
         <v>-3.4317</v>
@@ -2607,7 +2607,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.654010221971441</v>
+        <v>0.6540102219714409</v>
       </c>
       <c r="E10" t="n">
         <v>3.2821</v>
@@ -2647,7 +2647,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6521564396861916</v>
+        <v>0.6521564396861915</v>
       </c>
       <c r="E12" t="n">
         <v>4.8858</v>
@@ -2667,7 +2667,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.6507996223182585</v>
+        <v>0.6507996223182583</v>
       </c>
       <c r="E13" t="n">
         <v>1.4579</v>
@@ -2707,7 +2707,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.6454327112209287</v>
+        <v>0.6454327112209286</v>
       </c>
       <c r="E15" t="n">
         <v>3.3062</v>
@@ -2727,7 +2727,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.6452255059713194</v>
+        <v>0.6452255059713192</v>
       </c>
       <c r="E16" t="n">
         <v>1.9704</v>
@@ -2767,7 +2767,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.6439928680326992</v>
+        <v>0.6439928680326991</v>
       </c>
       <c r="E18" t="n">
         <v>4.5011</v>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.641936492236581</v>
+        <v>0.6419364922365811</v>
       </c>
       <c r="E19" t="n">
         <v>-0.9429999999999999</v>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.7237525485708562</v>
+        <v>0.7237525485708559</v>
       </c>
       <c r="E2" t="n">
         <v>7.4005</v>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6206435556080042</v>
+        <v>0.6206435556080043</v>
       </c>
       <c r="E6" t="n">
         <v>-0.7487</v>
@@ -3073,7 +3073,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6150296857988886</v>
+        <v>0.6150296857988885</v>
       </c>
       <c r="E11" t="n">
         <v>5.1363</v>
@@ -3133,7 +3133,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6118179196549234</v>
+        <v>0.6118179196549235</v>
       </c>
       <c r="E14" t="n">
         <v>-2.3013</v>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.6087580211239654</v>
+        <v>0.6087580211239655</v>
       </c>
       <c r="E16" t="n">
         <v>-1.2188</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.606515054803266</v>
+        <v>0.6065150548032661</v>
       </c>
       <c r="E18" t="n">
         <v>-1.9417</v>
@@ -3233,7 +3233,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.6055013573538864</v>
+        <v>0.6055013573538863</v>
       </c>
       <c r="E19" t="n">
         <v>0.45</v>
@@ -3253,7 +3253,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.605011653510804</v>
+        <v>0.6050116535108041</v>
       </c>
       <c r="E20" t="n">
         <v>-6.0995</v>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6278165378897702</v>
+        <v>0.6278165378897703</v>
       </c>
       <c r="E4" t="n">
         <v>11.9036</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6060420404692912</v>
+        <v>0.6060420404692913</v>
       </c>
       <c r="E10" t="n">
         <v>4.7515</v>
@@ -4142,7 +4142,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.5994006898313757</v>
+        <v>0.5994006898313758</v>
       </c>
       <c r="E12" t="n">
         <v>-0.6647</v>
@@ -4162,7 +4162,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.5988491443018789</v>
+        <v>0.5988491443018787</v>
       </c>
       <c r="E13" t="n">
         <v>33.2761</v>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.5957238766512216</v>
+        <v>0.5957238766512215</v>
       </c>
       <c r="E15" t="n">
         <v>-3.3923</v>
@@ -4262,7 +4262,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.5889822204366317</v>
+        <v>0.5889822204366318</v>
       </c>
       <c r="E18" t="n">
         <v>7.44</v>
@@ -4408,7 +4408,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.6184895238364055</v>
+        <v>0.6184895238364058</v>
       </c>
       <c r="E3" t="n">
         <v>14.2568</v>
@@ -4428,7 +4428,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6118036867163529</v>
+        <v>0.6118036867163528</v>
       </c>
       <c r="E4" t="n">
         <v>3.8871</v>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6061415382358432</v>
+        <v>0.6061415382358433</v>
       </c>
       <c r="E6" t="n">
         <v>-94.9173</v>
@@ -4488,7 +4488,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6025844949362948</v>
+        <v>0.6025844949362947</v>
       </c>
       <c r="E7" t="n">
         <v>-1.9416</v>
@@ -4528,7 +4528,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.6022141646943331</v>
+        <v>0.6022141646943332</v>
       </c>
       <c r="E9" t="n">
         <v>8.6111</v>
@@ -4548,7 +4548,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6019069281308004</v>
+        <v>0.6019069281308006</v>
       </c>
       <c r="E10" t="n">
         <v>5.9241</v>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6006466263433248</v>
+        <v>0.6006466263433246</v>
       </c>
       <c r="E12" t="n">
         <v>1.2415</v>
@@ -4648,7 +4648,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.5976829695464563</v>
+        <v>0.5976829695464562</v>
       </c>
       <c r="E15" t="n">
         <v>-4.8667</v>
@@ -4688,7 +4688,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.5960586487923984</v>
+        <v>0.5960586487923986</v>
       </c>
       <c r="E17" t="n">
         <v>2.2351</v>
@@ -4708,7 +4708,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.5932945290053445</v>
+        <v>0.5932945290053446</v>
       </c>
       <c r="E18" t="n">
         <v>3.4866</v>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.5908919880568068</v>
+        <v>0.5908919880568066</v>
       </c>
       <c r="E20" t="n">
         <v>11.4387</v>
@@ -4874,7 +4874,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.626224157821067</v>
+        <v>0.6262241578210671</v>
       </c>
       <c r="E4" t="n">
         <v>12.5696</v>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.621423457211002</v>
+        <v>0.6214234572110019</v>
       </c>
       <c r="E7" t="n">
         <v>3.1269</v>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6113145694477686</v>
+        <v>0.6113145694477687</v>
       </c>
       <c r="E14" t="n">
         <v>0.1821</v>
@@ -5094,7 +5094,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.6074673188749943</v>
+        <v>0.6074673188749944</v>
       </c>
       <c r="E15" t="n">
         <v>6.7078</v>
@@ -5194,7 +5194,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.5992419811216243</v>
+        <v>0.5992419811216244</v>
       </c>
       <c r="E20" t="n">
         <v>3.6606</v>
@@ -5380,7 +5380,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6113374455829966</v>
+        <v>0.6113374455829969</v>
       </c>
       <c r="E7" t="n">
         <v>4.3062</v>
@@ -5400,7 +5400,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6102505900093074</v>
+        <v>0.6102505900093073</v>
       </c>
       <c r="E8" t="n">
         <v>-1.3456</v>
@@ -5560,7 +5560,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.6020418943203895</v>
+        <v>0.6020418943203893</v>
       </c>
       <c r="E16" t="n">
         <v>2.8772</v>
@@ -5660,7 +5660,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.5962812933892476</v>
+        <v>0.5962812933892477</v>
       </c>
       <c r="E21" t="n">
         <v>3.1558</v>
@@ -5726,7 +5726,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.6593432261743363</v>
+        <v>0.6593432261743364</v>
       </c>
       <c r="E2" t="n">
         <v>0.3655</v>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.6295459249370924</v>
+        <v>0.6295459249370923</v>
       </c>
       <c r="E3" t="n">
         <v>8.1038</v>
@@ -5866,7 +5866,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.6161188024740962</v>
+        <v>0.6161188024740963</v>
       </c>
       <c r="E9" t="n">
         <v>-6.0081</v>
@@ -5926,7 +5926,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6119014277699598</v>
+        <v>0.6119014277699597</v>
       </c>
       <c r="E12" t="n">
         <v>1.7496</v>
@@ -5946,7 +5946,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.6110692383606355</v>
+        <v>0.6110692383606356</v>
       </c>
       <c r="E13" t="n">
         <v>15.7153</v>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.607421198802899</v>
+        <v>0.6074211988028989</v>
       </c>
       <c r="E16" t="n">
         <v>-6.2664</v>
@@ -6252,7 +6252,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.649459763900218</v>
+        <v>0.6494597639002176</v>
       </c>
       <c r="E6" t="n">
         <v>10.5769</v>
@@ -6372,7 +6372,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6398436543991912</v>
+        <v>0.6398436543991911</v>
       </c>
       <c r="E12" t="n">
         <v>5.9836</v>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.6278601283865833</v>
+        <v>0.6278601283865832</v>
       </c>
       <c r="E15" t="n">
         <v>-1.6949</v>
